--- a/sheets/대금율보/검수/미움인지 그립움인지.xlsx
+++ b/sheets/대금율보/검수/미움인지 그립움인지.xlsx
@@ -5919,8 +5919,7 @@
       <c r="C5" s="23"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="E5" s="23"/>
@@ -6024,8 +6023,7 @@
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無
-‹</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="C7" s="22"/>
@@ -6089,11 +6087,7 @@
         </is>
       </c>
       <c r="E8" s="23"/>
-      <c r="F8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F8" s="21"/>
       <c r="G8" s="23"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
@@ -6126,8 +6120,7 @@
       <c r="C9" s="23"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="E9" s="23"/>
@@ -6140,8 +6133,7 @@
       <c r="G9" s="23"/>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋
-‹</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="I9" s="23" t="inlineStr">
@@ -6152,8 +6144,7 @@
       <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△汰
-無南
-‹</t>
+無南</t>
         </is>
       </c>
       <c r="K9" s="23"/>
@@ -6325,8 +6316,7 @@
       <c r="E13" s="23"/>
       <c r="F13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="G13" s="23"/>
@@ -6420,8 +6410,7 @@
       <c r="D15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-林南
-‹</t>
+林南</t>
         </is>
       </c>
       <c r="E15" s="22"/>
@@ -6455,8 +6444,7 @@
       <c r="L15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-林南
-‹</t>
+林南</t>
         </is>
       </c>
       <c r="M15" s="22"/>
@@ -6541,8 +6529,7 @@
       <c r="I17" s="23"/>
       <c r="J17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="K17" s="23" t="inlineStr">
@@ -6628,8 +6615,7 @@
       </c>
       <c r="F19" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無
-‹</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="G19" s="22"/>
@@ -6657,8 +6643,7 @@
       <c r="L19" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△
-林
-‹</t>
+林</t>
         </is>
       </c>
       <c r="M19" s="22"/>
@@ -6782,8 +6767,7 @@
       <c r="F22" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南林
-夾林
-‹</t>
+夾林</t>
         </is>
       </c>
       <c r="G22" s="24"/>
@@ -6808,8 +6792,7 @@
       <c r="L22" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-汰
-‹</t>
+汰</t>
         </is>
       </c>
       <c r="M22" s="24"/>
@@ -6914,8 +6897,7 @@
       <c r="C25" s="23"/>
       <c r="D25" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="E25" s="23"/>
@@ -6927,8 +6909,7 @@
       <c r="G25" s="23"/>
       <c r="H25" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="I25" s="23" t="inlineStr">

--- a/sheets/대금율보/검수/미움인지 그립움인지.xlsx
+++ b/sheets/대금율보/검수/미움인지 그립움인지.xlsx
@@ -5764,24 +5764,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="129.03" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="96.3" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="M3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="96.3" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="M4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="96.3" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
       </c>
       <c r="M5" s="23"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="96.3" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -6019,7 +6019,7 @@
       </c>
       <c r="M6" s="24"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="96.3" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="M7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="96.3" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="M8" s="23"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="96.3" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -6155,7 +6155,7 @@
       </c>
       <c r="M9" s="23"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="96.3" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="M10" s="24"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="96.3" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="M11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="96.3" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="23"/>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="M12" s="23"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="96.3" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
       </c>
       <c r="M13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="96.3" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="M14" s="24"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="96.3" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
       </c>
       <c r="M15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="96.3" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="M16" s="23"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="96.3" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="25" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
       </c>
       <c r="M17" s="23"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="96.3" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -6593,7 +6593,7 @@
       </c>
       <c r="M18" s="24"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="96.3" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
       </c>
       <c r="M19" s="22"/>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="96.3" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
       </c>
       <c r="M20" s="23"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="96.3" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21" t="inlineStr">
         <is>
@@ -6753,7 +6753,7 @@
       </c>
       <c r="M21" s="23"/>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="96.3" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="24"/>
@@ -6797,7 +6797,7 @@
       </c>
       <c r="M22" s="24"/>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="96.3" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="25" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
       </c>
       <c r="M23" s="22"/>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="96.3" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="23"/>
@@ -6891,7 +6891,7 @@
       </c>
       <c r="M24" s="23"/>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="96.3" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="23"/>
@@ -6931,7 +6931,7 @@
       </c>
       <c r="M25" s="23"/>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="96.3" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="24"/>
@@ -6981,6 +6981,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="52"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="31"/>
 </worksheet>
 </file>